--- a/tests/fixtures/06_merged_cells/data-export-control.xlsx
+++ b/tests/fixtures/06_merged_cells/data-export-control.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -514,179 +514,180 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>item.category</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>item.name</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>item.price</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Laptop 15"</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Wireless Mouse</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>29.99</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Hardware</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Keyboard</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>89.98999999999999</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Office Suite</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Design Suite</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Dev Tools</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n">
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
         <v>2369.98</v>
       </c>
     </row>
